--- a/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
@@ -425,195 +425,195 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Xiaomi</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Sansei</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kodak</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Alcatel</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Philco</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Quantum</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Philco</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Kodak</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Alcatel</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Blackview</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>BLU</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>iPro</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Energizer</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Sansei</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>ZTE</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Energizer</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>TCL</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>iPro</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>BLU - IPRO - NOKIA - GENERICO</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>RugGear</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Hyundai</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Realme</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Excess</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>P&amp;S Mobile</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Positivo</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Blackview</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>P&amp;S Mobile</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Ulefone</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Hyundai</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>BLU</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>RugGear</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Excess</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>BLU,IPRO, OTRAS MARCAS</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>IPRO - BLU - EXC SEGUN STOCK</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Doogee</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Panacom</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Noblex</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Realme</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Panacom</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>BLU - IPRO - NOKIA - GENERICO</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Luo</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Huawei</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>T-36</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>BLU,IPRO, OTRAS MARCAS</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Asus</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Sony</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>OnePlus</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>Kanji</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>IPRO - BLU - EXC SEGUN STOCK</t>
-        </is>
-      </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Logic</t>
@@ -621,278 +621,228 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Doogee</t>
+          <t>BlackBerry</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Infinix</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>Huawei</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>BlackBerry</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>Cyrus</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>Luo</t>
+          <t>iPhone</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mejores en calidad</t>
+          <t>Buena relacion precio - calidad</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106</v>
+        <v>38</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>55</v>
-      </c>
-      <c r="F2" t="n">
-        <v>158</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>14</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D2" t="n">
+        <v>71</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="J2" t="n">
+        <v>13</v>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>24</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>2</v>
+      </c>
       <c r="O2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7</v>
-      </c>
-      <c r="R2" t="n">
-        <v>2</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>10</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="n">
+        <v>2</v>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>8</v>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>2</v>
+      </c>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>4</v>
-      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+          <t>Mejor relacion precio - calidad</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>124</v>
+      </c>
+      <c r="C3" t="n">
+        <v>30</v>
+      </c>
       <c r="D3" t="n">
+        <v>41</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>27</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
-        <v>2</v>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="n">
-        <v>3</v>
-      </c>
-      <c r="W3" t="n">
-        <v>8</v>
-      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1</v>
-      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1</v>
-      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Caros y buena calidad</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
+          <t>Baratos y calidad acorde</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>6</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
       <c r="Q4" t="n">
-        <v>74</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>12</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>9</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
+      </c>
       <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="W4" t="n">
+        <v>1</v>
+      </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
@@ -901,17 +851,23 @@
       <c r="AH4" t="n">
         <v>1</v>
       </c>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
       <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
+      <c r="AL4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
       <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -920,43 +876,45 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>94</v>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
         <v>5</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" t="n">
-        <v>22</v>
       </c>
       <c r="G5" t="n">
         <v>3</v>
       </c>
       <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="n">
         <v>7</v>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="n">
-        <v>8</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
@@ -965,36 +923,91 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2</v>
+      </c>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="n">
-        <v>2</v>
-      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+      <c r="AF5" t="n">
+        <v>2</v>
+      </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="n">
+        <v>7</v>
+      </c>
       <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Calidad a alto costo</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>73</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
@@ -633,378 +633,634 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Buena relacion precio - calidad</t>
+          <t>Escalon abajo de numero 1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J2" t="n">
         <v>13</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
       <c r="V2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
       <c r="X2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y2" t="n">
         <v>3</v>
       </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
       <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
         <v>2</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Mejor relacion precio - calidad</t>
+          <t>Baratos pero calidad acorde</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
       <c r="F3" t="n">
-        <v>6</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
       <c r="I3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>9</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baratos y calidad acorde</t>
+          <t>Los numero 1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>102</v>
       </c>
       <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>55</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>5</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
       <c r="W4" t="n">
-        <v>1</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero buenos</t>
+          <t>Baratos y calidad media</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
       <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
         <v>5</v>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
       <c r="I5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
       <c r="L5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
+        <v>4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
         <v>5</v>
       </c>
-      <c r="O5" t="n">
-        <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>2</v>
       </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
       <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
         <v>2</v>
       </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="n">
         <v>2</v>
       </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
       <c r="AK5" t="n">
         <v>7</v>
       </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Calidad a alto costo</t>
+          <t>Caros y calidad media</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
       <c r="F6" t="n">
-        <v>73</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
       <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>

--- a/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO6"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,124 +526,159 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
+          <t>Konka</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
           <t>BLU - IPRO - NOKIA - GENERICO</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>RugGear</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Hyundai</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Realme</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Google</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Excess</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>P&amp;S Mobile</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Noblex</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Positivo</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Sony</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>celular adultos</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>BLU,IPRO, OTRAS MARCAS</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>IPRO - BLU - EXC SEGUN STOCK</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Doogee</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Sony</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Philips</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Panacom</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Noblex</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Luo</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Microsoft</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>blu - nokia - energizer - lg</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Huawei</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>T-36</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Logic</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>BlackBerry</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>Sony Ericsson</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>Rokit</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>iPhone</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>Sky Devices</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Escalon abajo de numero 1</t>
+          <t>Los numero 1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -658,29 +693,29 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" t="n">
+        <v>4</v>
+      </c>
+      <c r="P2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
@@ -700,44 +735,44 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
         <v>2</v>
       </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
@@ -754,62 +789,83 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
+          <t>Totalmente basicos</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>5</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8</v>
       </c>
       <c r="R3" t="n">
         <v>12</v>
@@ -818,25 +874,25 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U3" t="n">
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>1</v>
@@ -845,10 +901,10 @@
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -863,13 +919,13 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
@@ -878,41 +934,62 @@
         <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Baratos y calidad alta</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,10 +1004,10 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -945,7 +1022,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1008,38 +1085,59 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Baratos y calidad media</t>
+          <t>Caros y calidad media</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>103</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1048,19 +1146,19 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1072,13 +1170,13 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -1087,7 +1185,7 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
         <v>0</v>
@@ -1105,10 +1203,10 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1123,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1135,20 +1233,41 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Caros y calidad media</t>
+          <t>Baratos y calidad media</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -1157,10 +1276,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1169,22 +1288,22 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1199,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1217,13 +1336,13 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1232,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1262,7 +1381,28 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R5"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,67 +451,42 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ZTE</t>
+          <t>TCL</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>TCL</t>
+          <t>Alcatel</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Alcatel</t>
+          <t>CAT</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>CAT</t>
+          <t>LG</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>LG</t>
+          <t>Ulefone</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Ulefone</t>
+          <t>BLU</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Blackview</t>
+          <t>iPro</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>BLU</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>iPro</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
           <t>Nokia</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Realme</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Sony</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Huawei</t>
         </is>
       </c>
     </row>
@@ -522,32 +497,32 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" t="n">
         <v>68</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
         <v>4</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
@@ -555,53 +530,38 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Caros y calidad media</t>
+          <t>Baratos pero calidad acorde</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
         <v>4</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" t="n">
-        <v>37</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>11</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -610,141 +570,53 @@
         <v>6</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Baratos y calidad media</t>
+          <t>Escalon debajo de numero 1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>43</v>
+      </c>
+      <c r="F4" t="n">
         <v>10</v>
       </c>
-      <c r="D4" t="n">
+      <c r="G4" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
         <v>3</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G4" t="n">
-        <v>11</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>6</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Muy baratos pero calidad acorde</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>7</v>
-      </c>
-      <c r="N5" t="n">
-        <v>14</v>
-      </c>
-      <c r="O5" t="n">
-        <v>8</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
@@ -431,14 +431,14 @@
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Motorola</t>
-        </is>
-      </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Xiaomi</t>
@@ -451,83 +451,83 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Alcatel</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>TCL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Alcatel</t>
-        </is>
-      </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>iPro</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>CAT</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Ulefone</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>BLU</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>iPro</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Google</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Baratos pero calidad acorde</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
         <v>6</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -536,29 +536,29 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
+          <t>Los numero 1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>3</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
       <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
         <v>5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
@@ -567,56 +567,56 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Escalon debajo de numero 1</t>
+          <t>Calidad a alto costo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
       <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>6</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
@@ -425,174 +425,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Xiaomi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Motorola</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>iPro</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Xiaomi</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Alcatel</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Blackview</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>BLU</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Nokia</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ZTE</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Alcatel</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>TCL</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Ulefone</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>iPro</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>CAT</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Nokia</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Google</t>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Umidigi</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Baratos pero calidad acorde</t>
+          <t>Alta calidad a buen precio</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>64</v>
+      </c>
+      <c r="C2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
         <v>5</v>
       </c>
-      <c r="C2" t="n">
-        <v>12</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6</v>
-      </c>
-      <c r="L2" t="n">
-        <v>7</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
+      <c r="O2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Los numero 1</t>
+          <t>Baratos pero baja calidad</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
         <v>1</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Calidad a alto costo</t>
+          <t>Calidad media a precio alto</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -601,22 +623,28 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
         <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,42 +461,52 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>CAT</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Blackview</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>BLU</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>ZTE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Ulefone</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Umidigi</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Doogee</t>
         </is>
       </c>
     </row>
@@ -537,16 +547,22 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>2</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>5</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -577,14 +593,14 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
         <v>9</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
@@ -592,9 +608,15 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -623,28 +645,34 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
         <v>6</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>24</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>4</v>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
+++ b/data/modelling/clustering/celulares/df_brand_per_cluster.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,40 +471,45 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Panacom</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>BLU</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Nokia</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ZTE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Ulefone</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Apple</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Ulefone</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Umidigi</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Doogee</t>
         </is>
@@ -550,18 +555,21 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O2" t="n">
         <v>5</v>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>5</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -596,27 +604,30 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" t="n">
         <v>9</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
       <c r="M3" t="n">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -657,21 +668,24 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
+        <v>4</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>24</v>
       </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1</v>
-      </c>
       <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
         <v>3</v>
       </c>
     </row>
